--- a/layout/CATALOGOS/PosicionOperacion_V4.xlsx
+++ b/layout/CATALOGOS/PosicionOperacion_V4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\CATALOGOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C845E325-D865-477D-B58F-78E8532E6200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E987F1A-A1E9-48C2-8327-5A0B22B6DEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{5BA6DE08-EB35-4231-926C-48C1159161AE}"/>
+    <workbookView xWindow="410" yWindow="1240" windowWidth="25110" windowHeight="17750" xr2:uid="{5BA6DE08-EB35-4231-926C-48C1159161AE}"/>
   </bookViews>
   <sheets>
     <sheet name="PosicionOperacion_V4" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve"> Clave</t>
   </si>
@@ -47,53 +47,23 @@
     <t>Descripción</t>
   </si>
   <si>
-    <t>S01</t>
+    <t>OPERACIONES DE COMPRA EN DIRECTO</t>
   </si>
   <si>
-    <t>La “tasa de referencia” corresponde a la última conocida en la fecha de inicio del intervalo de cada flujo (a recibir, a entregar o ambos, en su caso). Esta tasa se utiliza en forma simple para determinar la tasa de interés del flujo.</t>
+    <t>OPERACIONES DE VENTA EN DIRECTO</t>
   </si>
   <si>
-    <t>S02</t>
+    <t>C</t>
   </si>
   <si>
-    <t>La “tasa de referencia” corresponde a la conocida posterior a la fecha de inicio y hasta la fecha final de cada flujo (a recibir, a entregar o ambos, en su caso). Esta tasa se utiliza en forma simple para determinar la tasa de interés del flujo.</t>
-  </si>
-  <si>
-    <t>C01</t>
-  </si>
-  <si>
-    <t>La “tasa de referencia” corresponde a la conocida (una o varias) antes de la fecha de inicio del intervalo de cada flujo (a recibir, a entregar o ambos, en su caso). Esta tasa se utiliza en forma compuesta para determinar la tasa de interés del flujo.</t>
-  </si>
-  <si>
-    <t>C02</t>
-  </si>
-  <si>
-    <t>La “tasa de referencia” corresponde a la conocida entre la fecha de inicio y la fecha final del intervalo de cada flujo  (a recibir, a entregar o ambos, en su caso). Esta tasa se utiliza en forma compuesta para determinar la tasa de interés del flujo.</t>
-  </si>
-  <si>
-    <t>P02</t>
-  </si>
-  <si>
-    <t>El precio del subyacente corresponde al último conocido en la fecha de inicio del intervalo de cada flujo (a recibir, a entregar o ambos, en su caso). Este precio se utiliza para determinar el importe del flujo.</t>
-  </si>
-  <si>
-    <t>P03</t>
-  </si>
-  <si>
-    <t>El precio del subyacente corresponde al conocido durante el periodo comprendido entre la fecha de inicio y la fecha final de cada flujo (a recibir, a entregar o ambos, en su caso). Este precio se utiliza para determinar el importe del flujo.</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>El precio del subyacente, o la tasa de interés, es fijo.</t>
+    <t>V</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,20 +77,73 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFDDDDDD"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -134,102 +157,38 @@
       <top style="medium">
         <color rgb="FFDDDDDD"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFDDDDDD"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Segoe UI"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFDDDDDD"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDDDDDD"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDDDDDD"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDDDDDD"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Segoe UI"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFDDDDDD"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDDDDDD"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDDDDDD"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDDDDDD"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -240,16 +199,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA714182-BB4E-406F-AECB-E0233854120A}" name="Table1" displayName="Table1" ref="A1:B8" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7828A23C-2085-433B-9319-F1324B692243}" name=" Clave" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{3DAF46EC-DD6D-468E-991C-AF0627F00AE4}" name="Descripción" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -569,80 +518,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74AD228B-2336-437D-82B9-F590B800ECF4}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="58.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="3" spans="1:2" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
+      <c r="B3" s="6" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>